--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:47</t>
+    <t xml:space="preserve">2026-09-09 22:35</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:35</t>
+    <t xml:space="preserve">2026-09-12 19:51</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_antofagasta.xlsx
@@ -45,18 +45,18 @@
     <t xml:space="preserve">Taltal</t>
   </si>
   <si>
+    <t xml:space="preserve">Tocopilla</t>
+  </si>
+  <si>
     <t xml:space="preserve">María Elena</t>
   </si>
   <si>
-    <t xml:space="preserve">Tocopilla</t>
+    <t xml:space="preserve">Calama</t>
   </si>
   <si>
     <t xml:space="preserve">Sierra Gorda</t>
   </si>
   <si>
-    <t xml:space="preserve">Calama</t>
-  </si>
-  <si>
     <t xml:space="preserve">Ollagüe</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:51</t>
+    <t xml:space="preserve">2026-09-24 00:30</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>14.53</v>
+        <v>7.31</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>7.02</v>
+        <v>5.5</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>-1.36</v>
+        <v>1.11</v>
       </c>
     </row>
     <row r="5">
@@ -547,16 +547,16 @@
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>2101</v>
+        <v>2301</v>
       </c>
       <c r="D5" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-3.44</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="6">
@@ -564,16 +564,16 @@
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>2302</v>
+        <v>2101</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-3.67</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="7">
@@ -584,13 +584,13 @@
         <v>10</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="D7" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-4.78</v>
+        <v>-1.84</v>
       </c>
     </row>
     <row r="8">
@@ -601,13 +601,13 @@
         <v>11</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>2103</v>
+        <v>2201</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-5.29</v>
+        <v>-1.85</v>
       </c>
     </row>
     <row r="9">
@@ -618,13 +618,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>2201</v>
+        <v>2103</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-8.32</v>
+        <v>-5.92</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-13.87</v>
+        <v>-11.41</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:30</t>
+    <t xml:space="preserve">2026-09-27 23:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2023</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>7.31</v>
+        <v>73.06</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2023</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>5.5</v>
+        <v>55.03</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>2023</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>1.11</v>
+        <v>11.06</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>2023</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>-0.41</v>
+        <v>-4.11</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>2023</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>-1.07</v>
+        <v>-10.74</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>2023</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-1.84</v>
+        <v>-18.42</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2023</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-1.85</v>
+        <v>-18.47</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2023</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-5.92</v>
+        <v>-59.22</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2023</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-11.41</v>
+        <v>-114.13</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:12</t>
+    <t xml:space="preserve">2026-10-01 20:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:58</t>
+    <t xml:space="preserve">2026-10-02 13:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_miginterna_a_2023_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_miginterna_a_2023_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:26</t>
+    <t xml:space="preserve">2026-10-05 08:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
